--- a/results/Int Task Remove ACC 0.2/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_5_permute.xlsx
@@ -440,257 +440,257 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6253667827256857</v>
+        <v>0.6202218511023773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6259108523665997</v>
+        <v>0.6176978769590977</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6343518417892257</v>
+        <v>0.6176978769590977</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6378442736498338</v>
+        <v>0.6171899181350586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6338235921252282</v>
+        <v>0.6171899181350586</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6435288040510145</v>
+        <v>0.6171899181350586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6296110074023735</v>
+        <v>0.6096609847729283</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6236059505123609</v>
+        <v>0.6128779426876627</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6249221038093129</v>
+        <v>0.6024728687395881</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6232379640927793</v>
+        <v>0.6014727710684262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6277982443952572</v>
+        <v>0.6035451880444995</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6339026920098112</v>
+        <v>0.5920000440208053</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.651816408480058</v>
+        <v>0.5914920851967661</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.650396393595523</v>
+        <v>0.5830669157510568</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6276651502416329</v>
+        <v>0.583859290247053</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6311304130114496</v>
+        <v>0.5817868732709797</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6184249080721776</v>
+        <v>0.5792064974708672</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6191608809113407</v>
+        <v>0.5792064974708672</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6151243794098186</v>
+        <v>0.5797505671117812</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6116161275722939</v>
+        <v>0.5797505671117812</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.613372488922577</v>
+        <v>0.5919322932500973</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6147158113103206</v>
+        <v>0.5922483488758875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6020983479817148</v>
+        <v>0.593284557363924</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6017822923559247</v>
+        <v>0.6036218805412908</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5992019165558122</v>
+        <v>0.6036218805412908</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6144448082274885</v>
+        <v>0.5923725013034284</v>
       </c>
     </row>
     <row r="28">
@@ -700,397 +700,397 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6138646277696996</v>
+        <v>0.5970930448503223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6092118349935138</v>
+        <v>0.5780506074183311</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6092118349935138</v>
+        <v>0.5774184961667508</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6302455260417454</v>
+        <v>0.5774184961667508</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6315616793386974</v>
+        <v>0.5936841837373389</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6386593463735798</v>
+        <v>0.5934042389284235</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5869297414190382</v>
+        <v>0.5994251157953527</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5713639158707384</v>
+        <v>0.5852590142916296</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5647153986152705</v>
+        <v>0.6102184670029673</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5674921484766737</v>
+        <v>0.6261161681539738</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5723684844049419</v>
+        <v>0.6308006008839928</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5725445676262744</v>
+        <v>0.6217433201867032</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5883452854405313</v>
+        <v>0.6215672369653708</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5859771036786261</v>
+        <v>0.6225312238196578</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5859771036786261</v>
+        <v>0.6256804309636842</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6018589848527161</v>
+        <v>0.6204563994557928</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5883566345544062</v>
+        <v>0.6335254199516046</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5910769827589765</v>
+        <v>0.6113110771478369</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6044190698128703</v>
+        <v>0.6123269947959153</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6180366308126378</v>
+        <v>0.6216415220743704</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6314217069342398</v>
+        <v>0.5944538600055851</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6201001060626279</v>
+        <v>0.5960860689283273</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6116095932340022</v>
+        <v>0.5997026532164764</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5995678395001438</v>
+        <v>0.6069313509297332</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5966239481434913</v>
+        <v>0.606071225663029</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6063202183431945</v>
+        <v>0.6153995094431506</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4782468439146051</v>
+        <v>0.6048589339536599</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4758425513358251</v>
+        <v>0.6017434302387166</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4758425513358251</v>
+        <v>0.6035833623366244</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4439594513356875</v>
+        <v>0.5872657439722448</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4432031876565662</v>
+        <v>0.5950429821894573</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4426591180156522</v>
+        <v>0.5850894654085887</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4701762482993525</v>
+        <v>0.5850014237979224</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4613425107541452</v>
+        <v>0.5896903273909831</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5202915277833186</v>
+        <v>0.5949707605557076</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5315883669519307</v>
+        <v>0.5930586068240502</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5333130883483806</v>
+        <v>0.5440087683941622</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5432057326093745</v>
+        <v>0.5088588431607488</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5286286556183616</v>
+        <v>0.510491052083491</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5358662950577017</v>
+        <v>0.523945942451051</v>
       </c>
     </row>
     <row r="68">
@@ -1100,227 +1100,227 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5036915572222321</v>
+        <v>0.5296913453721065</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5275336380857003</v>
+        <v>0.5050163083327257</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5379748228506498</v>
+        <v>0.5025759049370708</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.537166628377737</v>
+        <v>0.4942907078958192</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5385391833315221</v>
+        <v>0.4995597919466688</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5363739099691992</v>
+        <v>0.4995597919466688</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5321884943371361</v>
+        <v>0.5005079588240392</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5570619689130576</v>
+        <v>0.5005079588240392</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5548743412355265</v>
+        <v>0.5005079588240392</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5464130609729423</v>
+        <v>0.500544069640914</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5461850469578184</v>
+        <v>0.500544069640914</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.543920726783496</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.52656689993108</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5215303007583959</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5128612973206462</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5136694917935589</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5164417707919206</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5020001953423237</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5025442649832377</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5017721813271998</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5017721813271998</v>
+        <v>0.500228014015124</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5017721813271998</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5006840420453716</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
   </sheetData>
